--- a/erp-server/erp-server-srm/src/main/resources/excel/sysUserExport.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/sysUserExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27525" windowHeight="4440"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -73,16 +73,16 @@
     <t>{.email}</t>
   </si>
   <si>
+    <t>{.isSuperStr}</t>
+  </si>
+  <si>
+    <t>{.supplierName}</t>
+  </si>
+  <si>
+    <t>{.purchaseUserName}</t>
+  </si>
+  <si>
     <t>{.userStateStr}</t>
-  </si>
-  <si>
-    <t>{.supplierName}</t>
-  </si>
-  <si>
-    <t>{.purchaseUserName}</t>
-  </si>
-  <si>
-    <t>{.disabledStr}</t>
   </si>
   <si>
     <t>{.isBindWechatStr}</t>

--- a/erp-server/erp-server-srm/src/main/resources/excel/sysUserExport.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/sysUserExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>用户名</t>
   </si>
@@ -61,9 +61,6 @@
     <t>创建人</t>
   </si>
   <si>
-    <t>创建时间</t>
-  </si>
-  <si>
     <t>{.userName}</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
   </si>
   <si>
     <t>{.createUserName}</t>
-  </si>
-  <si>
-    <t>{.createTimeStr}</t>
   </si>
 </sst>
 </file>
@@ -723,7 +717,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -734,9 +728,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1086,8 +1077,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="36.375" customWidth="1"/>
     <col min="2" max="4" width="22.875" customWidth="1"/>
@@ -1096,10 +1087,9 @@
     <col min="8" max="8" width="19.5" customWidth="1"/>
     <col min="9" max="9" width="21.75" customWidth="1"/>
     <col min="10" max="10" width="20.25" customWidth="1"/>
-    <col min="11" max="11" width="29.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1130,47 +1120,38 @@
       <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:10">
+      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:11">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="11:11">
-      <c r="K7" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-srm/src/main/resources/excel/sysUserExport.xlsx
+++ b/erp-server/erp-server-srm/src/main/resources/excel/sysUserExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>用户名</t>
   </si>
@@ -46,9 +46,6 @@
     <t>关联供应商</t>
   </si>
   <si>
-    <t>采购员</t>
-  </si>
-  <si>
     <t>启用状态</t>
   </si>
   <si>
@@ -58,9 +55,6 @@
     <t>最近登录时间</t>
   </si>
   <si>
-    <t>创建人</t>
-  </si>
-  <si>
     <t>{.userName}</t>
   </si>
   <si>
@@ -76,9 +70,6 @@
     <t>{.supplierName}</t>
   </si>
   <si>
-    <t>{.purchaseUserName}</t>
-  </si>
-  <si>
     <t>{.userStateStr}</t>
   </si>
   <si>
@@ -86,9 +77,6 @@
   </si>
   <si>
     <t>{.lastLoginTimeStr}</t>
-  </si>
-  <si>
-    <t>{.createUserName}</t>
   </si>
 </sst>
 </file>
@@ -1077,19 +1065,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="36.375" customWidth="1"/>
     <col min="2" max="4" width="22.875" customWidth="1"/>
-    <col min="5" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="19.5" customWidth="1"/>
-    <col min="9" max="9" width="21.75" customWidth="1"/>
-    <col min="10" max="10" width="20.25" customWidth="1"/>
+    <col min="5" max="5" width="17.625" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19.5" customWidth="1"/>
+    <col min="8" max="8" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" ht="21.75" customHeight="1" spans="1:8">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1105,52 +1092,40 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+    </row>
+    <row r="2" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="1" ht="29.25" customHeight="1" spans="1:10">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
